--- a/esthetician_forms/009_covid_19_waxing_boutique_waiver_form--esthetician_forms.xlsx
+++ b/esthetician_forms/009_covid_19_waxing_boutique_waiver_form--esthetician_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>covid_19_waxing_boutique_waiver_form_1</t>
+          <t>medical_conditions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>covid_19_waxing_boutique_waiver_form_1</t>
+          <t>medical conditions</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>medical_conditions</t>
+          <t>medical_allergies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>medical_conditions</t>
+          <t>allergies</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>allergies</t>
+          <t>medical_facility_name</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>allergies</t>
+          <t>doctor's name</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>medical_facility_name</t>
+          <t>medical_facility_address</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>medical_facility_name</t>
+          <t>medical facility address</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>medical_facility_address</t>
+          <t>medical_facility_phone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>medical_facility_address</t>
+          <t>phone number</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>medical_facility_phone</t>
+          <t>medical_facility_email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>medical_facility_phone</t>
+          <t>email</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>medical_facility_email</t>
+          <t>medical_facility_license</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>medical_facility_email</t>
+          <t>license</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>medical_facility_license</t>
+          <t>medical_facility_state_license</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>medical_facility_license</t>
+          <t>state license</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>medical_facility_state_license</t>
+          <t>medical_facility_city</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>medical_facility_state_license</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>medical_facility_city</t>
+          <t>medical_facility_zip</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>medical_facility_city</t>
+          <t>zip code</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>medical_facility_zip</t>
+          <t>medical_facility_country</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>medical_facility_zip</t>
+          <t>country</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>medical_facility_country</t>
+          <t>medical_facility_state</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>medical_facility_country</t>
+          <t>state</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>medical_facility_state</t>
+          <t>medical_facility_federal_license</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>medical_facility_state</t>
+          <t>federal license</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -842,246 +842,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>medical_facility_federal_license</t>
+          <t>medical_facility_website</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>medical_facility_federal_license</t>
+          <t>website</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>medical_facility_city</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>medical_facility_city</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>medical_facility_state</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>medical_facility_state</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>medical_facility_address</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>medical_facility_address</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>medical_facility_license</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>medical_facility_license</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>medical_facility_fax_number</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>medical_facility_fax_number</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>medical_facility_country</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>medical_facility_country</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>medical_facility_state</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>medical_facility_state</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>medical_facility_phone_number</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>medical_facility_phone_number</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>medical_facility_email</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>medical_facility_email</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>medical_facility_website</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>medical_facility_website</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1102,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>high_blood_pressure</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>High Blood Pressure</t>
         </is>
       </c>
     </row>
@@ -1148,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'high_blood_pressure'}</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'High Blood Pressure'}</t>
+          <t>Diabetes</t>
         </is>
       </c>
     </row>
@@ -1165,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'diabetes'}</t>
+          <t>allergic_reaction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Diabetes'}</t>
+          <t>Allergic Reaction</t>
         </is>
       </c>
     </row>
@@ -1182,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'allergic_reaction'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Allergic Reaction'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
